--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_353_R36.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_353_R36.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6495</v>
+        <v>4.8325</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1918</v>
+        <v>5.3412</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5423</v>
+        <v>-0.5087</v>
       </c>
       <c r="G2" t="n">
         <v>3.23</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0444</v>
+        <v>0.1386</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1845</v>
+        <v>-0.0351</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1401</v>
+        <v>0.1737</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9038</v>
+        <v>1.7515</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8598</v>
+        <v>2.8627</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.956</v>
+        <v>-1.1112</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7415</v>
+        <v>1.3721</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8954</v>
+        <v>2.048</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1539</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8579</v>
+        <v>3.4483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8605</v>
+        <v>1.9662</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9974</v>
+        <v>1.4821</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.5995</v>
+        <v>-2.0762</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.756</v>
+        <v>0.0818</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8435</v>
+        <v>-2.1581</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1092</v>
+        <v>-0.4039</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0895</v>
+        <v>-0.5856</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0198</v>
+        <v>0.1817</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3476</v>
+        <v>0.7131</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6268</v>
+        <v>2.9044</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2792</v>
+        <v>-2.1913</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3721</v>
+        <v>-0.7415</v>
       </c>
       <c r="H4" t="n">
-        <v>2.048</v>
+        <v>-0.8954</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.1539</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4483</v>
+        <v>2.8579</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9662</v>
+        <v>0.8605</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4821</v>
+        <v>1.9974</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0762</v>
+        <v>-3.5995</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0818</v>
+        <v>-1.756</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1581</v>
+        <v>-1.8435</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8079</v>
+        <v>-0.0815</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8215</v>
+        <v>0.134</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0136</v>
+        <v>-0.2155</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5555</v>
+        <v>-0.8698</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4908</v>
+        <v>-0.1852</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0648</v>
+        <v>-0.6846</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6381</v>
+        <v>-0.924</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1224</v>
+        <v>-0.228</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5157</v>
+        <v>-0.696</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6797</v>
+        <v>0.2273</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9005</v>
+        <v>0.7093</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2208</v>
+        <v>-0.482</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9584</v>
+        <v>-1.1513</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.222</v>
+        <v>-0.9373</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7365</v>
+        <v>-0.214</v>
       </c>
       <c r="P5" t="n">
         <v>1.6237</v>
@@ -844,28 +844,28 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.995</v>
+        <v>-0.4973</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>-0.4125</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8061</v>
+        <v>-0.0848</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7941</v>
+        <v>-0.952</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0423</v>
+        <v>-0.652</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7519</v>
+        <v>-0.3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.924</v>
+        <v>-2.6381</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.228</v>
+        <v>-1.1224</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.696</v>
+        <v>-1.5157</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2273</v>
+        <v>-0.6797</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7093</v>
+        <v>-0.9005</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.482</v>
+        <v>0.2208</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1513</v>
+        <v>-1.9584</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9373</v>
+        <v>-0.222</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.214</v>
+        <v>-1.7365</v>
       </c>
       <c r="P6" t="n">
         <v>1.6237</v>
@@ -922,22 +922,22 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4216</v>
+        <v>0.5985</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2696</v>
+        <v>0.0277</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.152</v>
+        <v>0.5709</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3842</v>
+        <v>-2.0572</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2</v>
+        <v>-2.0074</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1842</v>
+        <v>-0.0498</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3327</v>
@@ -1000,13 +1000,13 @@
         <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6572</v>
+        <v>-0.3301</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3339</v>
+        <v>-0.1412</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3233</v>
+        <v>-0.1889</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3943</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.115</v>
+        <v>-3.679</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8619</v>
+        <v>-2.005</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2531</v>
+        <v>-1.674</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.1537</v>
+        <v>-3.8476</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.2196</v>
+        <v>-2.9542</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9341</v>
+        <v>-0.8934</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5255</v>
+        <v>-1.27</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4852</v>
+        <v>-1.2198</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0403</v>
+        <v>-0.0502</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.6282</v>
+        <v>-2.5775</v>
       </c>
       <c r="N8" t="n">
         <v>-1.7344</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8938</v>
+        <v>-0.8431</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4252</v>
+        <v>-1.084</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4086</v>
+        <v>-0.735</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0167</v>
+        <v>-0.349</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0.7886</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1576</v>
+        <v>-4.4779</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3156</v>
+        <v>-1.0231</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.842</v>
+        <v>-3.4548</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8476</v>
+        <v>-5.1537</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.9542</v>
+        <v>-3.2196</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8934</v>
+        <v>-1.9341</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.27</v>
+        <v>-1.5255</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2198</v>
+        <v>-1.4852</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0502</v>
+        <v>-0.0403</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5775</v>
+        <v>-3.6282</v>
       </c>
       <c r="N9" t="n">
         <v>-1.7344</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8431</v>
+        <v>-1.8938</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5626</v>
+        <v>-0.7881</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0455</v>
+        <v>-0.5698</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5171</v>
+        <v>-0.2183</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7886</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8945</v>
+        <v>-4.4831</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2725</v>
+        <v>-2.962</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.622</v>
+        <v>-1.5212</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1966</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7701</v>
+        <v>-0.3587</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5228</v>
+        <v>-0.2122</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2473</v>
+        <v>-0.1465</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0877</v>
+        <v>-4.7458</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2168</v>
+        <v>-1.8748</v>
       </c>
       <c r="F11" t="n">
         <v>-2.871</v>
@@ -1312,10 +1312,10 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8962</v>
+        <v>-0.5542</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4832</v>
+        <v>-0.1412</v>
       </c>
       <c r="U11" t="n">
         <v>-0.4129</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.0877</v>
+        <v>-13.9677</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7215000000000007</v>
+        <v>0.3987999999999978</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.3665</v>
+        <v>-14.3666</v>
       </c>
       <c r="G12" t="n">
         <v>-16.2639</v>
@@ -1363,7 +1363,7 @@
         <v>-11.2764</v>
       </c>
       <c r="J12" t="n">
-        <v>9.525499999999999</v>
+        <v>9.525500000000001</v>
       </c>
       <c r="K12" t="n">
         <v>6.5825</v>
@@ -1381,7 +1381,7 @@
         <v>-14.2196</v>
       </c>
       <c r="P12" t="n">
-        <v>5.798799999999999</v>
+        <v>5.798800000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-9.2781</v>
@@ -1390,16 +1390,16 @@
         <v>15.077</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.481000000000001</v>
+        <v>-3.3607</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.7912</v>
+        <v>-2.6709</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6897</v>
+        <v>-0.6896</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1417999999999999</v>
+        <v>-0.1418</v>
       </c>
       <c r="W12" t="n">
         <v>2.8223</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9123</v>
+        <v>8.1653</v>
       </c>
       <c r="E13" t="n">
-        <v>7.1899</v>
+        <v>7.5438</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7224</v>
+        <v>0.6216</v>
       </c>
       <c r="G13" t="n">
         <v>4.4004</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0242</v>
+        <v>0.2289</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6563</v>
+        <v>-0.3025</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6322</v>
+        <v>0.5313</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5824</v>
+        <v>5.0371</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6824</v>
+        <v>5.0362</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1</v>
+        <v>0.0008</v>
       </c>
       <c r="G14" t="n">
         <v>6.397</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4951</v>
+        <v>-0.0404</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5149</v>
+        <v>-0.161</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0198</v>
+        <v>0.1206</v>
       </c>
       <c r="V14" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7195</v>
+        <v>2.1868</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3075</v>
+        <v>1.01</v>
       </c>
       <c r="F16" t="n">
-        <v>1.412</v>
+        <v>1.1768</v>
       </c>
       <c r="G16" t="n">
         <v>2.6679</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>2.768</v>
+        <v>1.2353</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8363</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9318</v>
+        <v>0.6965</v>
       </c>
       <c r="V16" t="n">
         <v>-0.7886</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1831</v>
+        <v>1.7386</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0872</v>
+        <v>1.441</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0959</v>
+        <v>0.2975</v>
       </c>
       <c r="G17" t="n">
         <v>0.5847</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1344</v>
+        <v>0.6899</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2161</v>
+        <v>0.1377</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3506</v>
+        <v>0.5522</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.384</v>
+        <v>0.1277</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7268</v>
+        <v>0.014</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3428</v>
+        <v>0.1137</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3487</v>
+        <v>-0.577</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9243</v>
+        <v>0.0888</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5756</v>
+        <v>-0.6657999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5379</v>
+        <v>0.1947</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1982</v>
+        <v>0.1211</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7361</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8866000000000001</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7261</v>
+        <v>-0.0323</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1605</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9647</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6528</v>
+        <v>-0.1808</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3119</v>
+        <v>0.1896</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1183</v>
+        <v>-0.1341</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1689</v>
+        <v>-0.2868</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2871</v>
+        <v>0.1527</v>
       </c>
       <c r="G19" t="n">
         <v>1.0847</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1211</v>
+        <v>0.8687</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4288</v>
+        <v>0.3108</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6923</v>
+        <v>0.5579</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0239</v>
+        <v>-0.3566</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.104</v>
+        <v>0.255</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0801</v>
+        <v>-0.6116</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.577</v>
+        <v>-0.3487</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0888</v>
+        <v>-0.9243</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6657999999999999</v>
+        <v>0.5756</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1947</v>
+        <v>0.5379</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1211</v>
+        <v>-0.1982</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>0.7361</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0323</v>
+        <v>-0.7261</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.1605</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1428</v>
+        <v>0.224</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>0.181</v>
       </c>
       <c r="U20" t="n">
-        <v>0.156</v>
+        <v>0.0431</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0795</v>
+        <v>-1.8272</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2219</v>
+        <v>-1.1039</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8577</v>
+        <v>-0.7232</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0198</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0597</v>
+        <v>0.1926</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0896</v>
+        <v>0.224</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8555</v>
+        <v>-3.9969</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3461</v>
+        <v>-3.7564</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5094</v>
+        <v>-0.2405</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0937</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5324</v>
+        <v>0.3262</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5816</v>
+        <v>0.0081</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0492</v>
+        <v>0.3181</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6778999999999999</v>
@@ -2209,7 +2209,7 @@
         <v>14.3666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7212</v>
+        <v>0.7214</v>
       </c>
       <c r="G23" t="n">
         <v>16.264</v>
@@ -2251,10 +2251,10 @@
         <v>4.480799999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6897999999999999</v>
+        <v>0.6896</v>
       </c>
       <c r="U23" t="n">
-        <v>3.7913</v>
+        <v>3.7912</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418000000000004</v>
